--- a/data/信用债发行汇总_2026-08-10.xlsx
+++ b/data/信用债发行汇总_2026-08-10.xlsx
@@ -1001,7 +1001,9 @@
           <t>1.40 ~ 1.67</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>1.59</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>国耀融汇融资租赁有限公司</t>
